--- a/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_phaseFlipped_A_000_B_100.xlsx
+++ b/plm python control/wrappers/multibeam parameters/multibeam diamond/multiBeam_innerCW_outerCCW_phaseFlipped_A_000_B_100.xlsx
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>1.076901077801928</v>
+        <v>1.163251963712884</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -652,7 +652,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>0.9542058541740658</v>
+        <v>0.9845733764160133</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -792,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="D33">
-        <v>0.8596981108972922</v>
+        <v>0.8958762313135574</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D44">
-        <v>1.00706779492958</v>
+        <v>0.9929129969454336</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1072,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="D55">
-        <v>0.8000766280078387</v>
+        <v>0.8116636731822621</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="D66">
-        <v>0.7613164793056466</v>
+        <v>0.7464301203421082</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D77">
-        <v>1.176327153103565</v>
+        <v>1.20265742720488</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1492,7 +1492,7 @@
         <v>8</v>
       </c>
       <c r="D88">
-        <v>0.8493345689586644</v>
+        <v>0.85595506564045</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="D99">
-        <v>0.7519790145598976</v>
+        <v>0.7232866397331975</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1772,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="D110">
-        <v>1.076962886884533</v>
+        <v>1.143816190773048</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1912,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="D121">
-        <v>0.9518170958731089</v>
+        <v>0.9173587496461394</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="D132">
-        <v>0.8534975024145471</v>
+        <v>0.8192254497074715</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="D138">
-        <v>39.6</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2178,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="D143">
-        <v>0.8264276674516406</v>
+        <v>0.8271484970525158</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="D154">
-        <v>0.871718881589572</v>
+        <v>0.7741764888153944</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2472,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="D165">
-        <v>0.8603710739283469</v>
+        <v>0.8146651860426058</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>8</v>
       </c>
       <c r="D176">
-        <v>1.203310800118084</v>
+        <v>1.12237181892834</v>
       </c>
     </row>
   </sheetData>
